--- a/rs.xlsx
+++ b/rs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelalbath/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{316C29F2-E999-5E4B-81BC-20A1905ADCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C88382-713B-F642-B038-F02384224B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="3340" windowWidth="25880" windowHeight="15240" xr2:uid="{6EF56752-A77E-CF4D-BC24-118EBA234D35}"/>
   </bookViews>
@@ -438,4882 +438,4882 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1">
-        <v>5487536002</v>
+        <v>4310224033606</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>5352327005</v>
+        <v>4311596658053</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>6175289002</v>
+        <v>4255582800487</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>3200035003</v>
+        <v>4003573020969</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>4950584001</v>
+        <v>5000357108577</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>2111589003</v>
+        <v>7610700945131</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>142047002</v>
+        <v>4008557069552</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>2969700009</v>
+        <v>42215165</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>6599602003</v>
+        <v>196214107809</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>2871064004</v>
+        <v>7610700946053</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>2675689001</v>
+        <v>42229889</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>2111588000</v>
+        <v>7610700945117</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>2112415006</v>
+        <v>7610700945087</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>2872802001</v>
+        <v>7610700946442</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>2872793008</v>
+        <v>7610700946398</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>2113569005</v>
+        <v>7610700945001</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>5600308000</v>
+        <v>7610700017890</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>2576115009</v>
+        <v>42212003</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>6019205005</v>
+        <v>4310224029180</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>3154689002</v>
+        <v>7610700947753</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>3709869000</v>
+        <v>13051823566</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>6376013008</v>
+        <v>5054563211446</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>6613581002</v>
+        <v>4250519677033</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>4030831009</v>
+        <v>7322541083087</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>5051218002</v>
+        <v>4311536513404</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>5882670002</v>
+        <v>4310224027506</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>6019305004</v>
+        <v>4310224029210</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>6366493003</v>
+        <v>4104450000507</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>6246458007</v>
+        <v>4104420247031</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>5051216006</v>
+        <v>4311536513398</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>2823916007</v>
+        <v>4005800086373</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>6423480009</v>
+        <v>4311596016723</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>6284900005</v>
+        <v>4000445010615</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>4581110002</v>
+        <v>4310224015268</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
-        <v>822896005</v>
+        <v>4103040802019</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
-        <v>6465460009</v>
+        <v>4103040049230</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
-        <v>5217161005</v>
+        <v>4044889004496</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
-        <v>2872817003</v>
+        <v>7610700946008</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
-        <v>6471462000</v>
+        <v>4260208910761</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
-        <v>5050982003</v>
+        <v>4311536512988</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
-        <v>6313511006</v>
+        <v>4000445010691</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
-        <v>5889474007</v>
+        <v>4310224027841</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
-        <v>4480737009</v>
+        <v>4310224004682</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
-        <v>6019259002</v>
+        <v>4310224029197</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
-        <v>4714818007</v>
+        <v>4017279817945</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
-        <v>5854212005</v>
+        <v>4002727763622</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
-        <v>1351881009</v>
+        <v>8718114202372</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
-        <v>5269498005</v>
+        <v>4260654781632</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
-        <v>5517565000</v>
+        <v>4008491101349</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
-        <v>3974650000</v>
+        <v>4104420216709</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
-        <v>4695416005</v>
+        <v>8001841923840</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
-        <v>2887954003</v>
+        <v>40099132</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
-        <v>6313561001</v>
+        <v>4000445010073</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
-        <v>2970605005</v>
+        <v>4104420022720</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
-        <v>5872212003</v>
+        <v>4002653094722</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
-        <v>264956006</v>
+        <v>4012700916181</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
-        <v>5596834006</v>
+        <v>4250752204560</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
-        <v>4767475008</v>
+        <v>4103040036742</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
-        <v>6193659005</v>
+        <v>5054563207111</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
-        <v>4432609006</v>
+        <v>4311596626601</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
-        <v>6389229007</v>
+        <v>4103040048301</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
-        <v>6005762004</v>
+        <v>4310224028732</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
-        <v>5478952006</v>
+        <v>4311596660247</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
-        <v>2969457008</v>
+        <v>4104420057326</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
-        <v>4432295001</v>
+        <v>4311596626441</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
-        <v>3613580000</v>
+        <v>3600542109772</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
-        <v>4561896005</v>
+        <v>4002727152648</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
-        <v>5571454005</v>
+        <v>4310224034382</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
-        <v>5474436007</v>
+        <v>4311596659951</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
-        <v>6194359001</v>
+        <v>4311596011445</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
-        <v>6199079003</v>
+        <v>4310224035013</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
-        <v>242236009</v>
+        <v>4009241527006</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
-        <v>6733759006</v>
+        <v>4260558064282</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
-        <v>4432168000</v>
+        <v>4311596626403</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
-        <v>3587155000</v>
+        <v>3600542117050</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
-        <v>4695433000</v>
+        <v>8001841923765</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
-        <v>5166844006</v>
+        <v>3600542453158</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
-        <v>639120005</v>
+        <v>3600540299178</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
-        <v>5000011005</v>
+        <v>4065331000989</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
-        <v>6210892004</v>
+        <v>4008617121626</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
-        <v>4624439006</v>
+        <v>4310224018221</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
-        <v>5540298003</v>
+        <v>4260718297963</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
-        <v>4433883005</v>
+        <v>4311596627271</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
-        <v>4433391001</v>
+        <v>4311596627172</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
-        <v>2627083000</v>
+        <v>4045612001256</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
-        <v>6149946009</v>
+        <v>4103040047144</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
-        <v>792942007</v>
+        <v>7702018842384</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
-        <v>6645387009</v>
+        <v>4003573023144</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
-        <v>5710203002</v>
+        <v>4008491102148</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
-        <v>6113442003</v>
+        <v>4310224029883</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
-        <v>5980954000</v>
+        <v>4260556679501</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
-        <v>2596314008</v>
+        <v>3600541544024</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
-        <v>3587174001</v>
+        <v>3600542117326</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
-        <v>4510363002</v>
+        <v>4310224013806</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
-        <v>6696186006</v>
+        <v>4260289421712</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
-        <v>6602425003</v>
+        <v>4000445010714</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
-        <v>5406341007</v>
+        <v>3616303440800</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
-        <v>5648166000</v>
+        <v>4311596000524</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
-        <v>3070312008</v>
+        <v>4015000962346</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
-        <v>5158369009</v>
+        <v>4311536138447</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
-        <v>3303712001</v>
+        <v>3600541980273</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
-        <v>5999073004</v>
+        <v>4310224028640</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
-        <v>5527518001</v>
+        <v>4750746032464</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
-        <v>6556805003</v>
+        <v>4059729490438</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
-        <v>6005813001</v>
+        <v>4310224028794</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
-        <v>1616504009</v>
+        <v>4001638089494</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
-        <v>5051215003</v>
+        <v>4311536513381</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
-        <v>5352304002</v>
+        <v>4311596658022</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
-        <v>3303640007</v>
+        <v>3600541979833</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
-        <v>6406407009</v>
+        <v>4000417670915</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
-        <v>4260866004</v>
+        <v>3600542317009</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
-        <v>2673107008</v>
+        <v>4009077031333</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
-        <v>6214489004</v>
+        <v>4262354077503</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
-        <v>5660374009</v>
+        <v>4260229233313</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
-        <v>4114273006</v>
+        <v>4547410364866</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
-        <v>5417415007</v>
+        <v>4008455088310</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
-        <v>2292858004</v>
+        <v>4012346277608</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
-        <v>5000050000</v>
+        <v>4065331000767</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
-        <v>3112037003</v>
+        <v>4021457619313</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
-        <v>5108520007</v>
+        <v>3616302035397</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
-        <v>5872648008</v>
+        <v>4260044269474</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
-        <v>6313563007</v>
+        <v>4000445010080</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
-        <v>5957557003</v>
+        <v>4311536012525</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
-        <v>5508362009</v>
+        <v>8001090941848</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
-        <v>4091134000</v>
+        <v>4260350921387</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
-        <v>660094001</v>
+        <v>3600540244901</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
-        <v>4714475004</v>
+        <v>3600542383523</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
-        <v>4897400004</v>
+        <v>4036581534616</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
-        <v>6538618003</v>
+        <v>4250519672885</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
-        <v>976363006</v>
+        <v>4009775084341</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
-        <v>6349808006</v>
+        <v>4311596015290</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
-        <v>6008085003</v>
+        <v>4260526594100</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
-        <v>2458576003</v>
+        <v>3600541334496</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
-        <v>5817075009</v>
+        <v>9120124604531</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
-        <v>3303609006</v>
+        <v>3600541979314</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
-        <v>5668680005</v>
+        <v>4311596000784</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
-        <v>242280006</v>
+        <v>4026600501002</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
-        <v>5846118003</v>
+        <v>4250752205628</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
-        <v>5800232002</v>
+        <v>5060926680828</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
-        <v>6520693003</v>
+        <v>4018852034544</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
-        <v>1409477002</v>
+        <v>4008491445863</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
-        <v>5787911006</v>
+        <v>3600541943506</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
-        <v>2807297001</v>
+        <v>4008871209870</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
-        <v>6507821003</v>
+        <v>42467014</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
-        <v>3717046006</v>
+        <v>4062700888728</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
-        <v>3309381009</v>
+        <v>3600541970397</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
-        <v>3996886007</v>
+        <v>4005784030126</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
-        <v>2463198009</v>
+        <v>4250587753509</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
-        <v>3643859004</v>
+        <v>5054563041463</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
-        <v>3527688003</v>
+        <v>3600523528738</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
-        <v>4721713001</v>
+        <v>7611916154317</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
-        <v>5417978003</v>
+        <v>4311596658909</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
-        <v>1485654001</v>
+        <v>4008491445887</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
-        <v>4275317009</v>
+        <v>4015533037429</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
-        <v>4504481004</v>
+        <v>4250519646534</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
-        <v>5815556007</v>
+        <v>4036581252442</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
-        <v>5647261001</v>
+        <v>4015533051029</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
-        <v>5863630003</v>
+        <v>4260697141479</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
-        <v>3082152001</v>
+        <v>4002448100003</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
-        <v>6374329004</v>
+        <v>4008491111317</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
-        <v>3303713004</v>
+        <v>3600541980075</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
-        <v>2936956000</v>
+        <v>4002029030415</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
-        <v>591382000</v>
+        <v>3600540134387</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
-        <v>5491878002</v>
+        <v>3600542511148</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
-        <v>3303637001</v>
+        <v>3600541979635</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
-        <v>6627602007</v>
+        <v>3600531702243</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
-        <v>6593250008</v>
+        <v>3337875784054</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
-        <v>4774317001</v>
+        <v>4310224045043</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
-        <v>5579086000</v>
+        <v>4250752204621</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
-        <v>5079853007</v>
+        <v>4013283210314</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
-        <v>5880694002</v>
+        <v>4311596005017</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
-        <v>5676352004</v>
+        <v>4260697377045</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
-        <v>5406307007</v>
+        <v>3616303441067</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
-        <v>512054005</v>
+        <v>3168070203121</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
-        <v>6006161000</v>
+        <v>4310224028886</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
-        <v>6264895000</v>
+        <v>3600542545228</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
-        <v>4447310001</v>
+        <v>4005808782734</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
-        <v>1573805003</v>
+        <v>4043978230020</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
-        <v>5473838006</v>
+        <v>4311596633173</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
-        <v>3414970004</v>
+        <v>4009900519939</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
-        <v>616527009</v>
+        <v>4009932001037</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
-        <v>3679863002</v>
+        <v>4006581082608</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
-        <v>5504280006</v>
+        <v>4262378220404</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
-        <v>6539320002</v>
+        <v>4104420254893</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
-        <v>3488773006</v>
+        <v>4008455036717</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
-        <v>5980658005</v>
+        <v>4013283820490</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
-        <v>6170371005</v>
+        <v>8720294032168</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
-        <v>4516696007</v>
+        <v>4310224047306</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
-        <v>6436457005</v>
+        <v>4001638580519</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
-        <v>1010474007</v>
+        <v>4000211055000</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
-        <v>4303419008</v>
+        <v>4009932131130</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
-        <v>6149945006</v>
+        <v>4103040047120</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
-        <v>6501667003</v>
+        <v>9120111881662</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
-        <v>6266879004</v>
+        <v>5000204364354</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
-        <v>4341612007</v>
+        <v>3600542297790</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
-        <v>4709751003</v>
+        <v>4008491130608</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
-        <v>237637006</v>
+        <v>4002441020056</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
-        <v>2327722001</v>
+        <v>4048882245399</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
-        <v>5051208005</v>
+        <v>4311536513145</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
-        <v>3297786008</v>
+        <v>3600542020060</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
-        <v>6697521008</v>
+        <v>4010160003458</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
-        <v>3654605009</v>
+        <v>3600523610143</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
-        <v>5817092004</v>
+        <v>9120124604470</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
-        <v>5985058006</v>
+        <v>4008455096216</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
-        <v>2521749006</v>
+        <v>3600522471752</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
-        <v>6342586008</v>
+        <v>4103040048189</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
-        <v>6529646004</v>
+        <v>3600524187286</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
-        <v>6367279002</v>
+        <v>3600551153032</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
-        <v>2763628002</v>
+        <v>5411188115533</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
-        <v>6322153008</v>
+        <v>9120111881518</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
-        <v>4721353003</v>
+        <v>4310224045913</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
-        <v>6501690003</v>
+        <v>9120111881686</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
-        <v>1030980001</v>
+        <v>4006581020631</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
-        <v>6375370005</v>
+        <v>4059729491626</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
-        <v>6627569001</v>
+        <v>3600531702199</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
-        <v>210300002</v>
+        <v>4006581003313</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
-        <v>4083216000</v>
+        <v>4260350921370</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
-        <v>3997640006</v>
+        <v>4007573450443</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
-        <v>1097978001</v>
+        <v>4260044260464</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
-        <v>3572437007</v>
+        <v>4104420206274</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
-        <v>5759461001</v>
+        <v>4008137009909</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
-        <v>5406353000</v>
+        <v>3616303441586</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
-        <v>2305542007</v>
+        <v>4250587705461</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
-        <v>452432000</v>
+        <v>4002441020292</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
-        <v>6717616008</v>
+        <v>4063528094575</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
-        <v>4784098000</v>
+        <v>4310224046002</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
-        <v>4252027006</v>
+        <v>4048882250232</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
-        <v>5883192000</v>
+        <v>4057599005578</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
-        <v>5881720003</v>
+        <v>4005240050729</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
-        <v>5399548009</v>
+        <v>3600542461511</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
-        <v>4808683007</v>
+        <v>4311596691548</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
-        <v>6474696000</v>
+        <v>4025089004165</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
-        <v>5051212004</v>
+        <v>4311536513183</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
-        <v>3063845005</v>
+        <v>3600541901643</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
-        <v>4320546004</v>
+        <v>4005900691774</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
-        <v>2667468005</v>
+        <v>4000158940445</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
-        <v>6186448009</v>
+        <v>4310224034627</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
-        <v>5746196004</v>
+        <v>731509865745</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
-        <v>5051014002</v>
+        <v>4311536513282</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
-        <v>5767154007</v>
+        <v>5037156288278</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
-        <v>6627591008</v>
+        <v>3600531702229</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
-        <v>6267727007</v>
+        <v>4103040048967</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
-        <v>6747966001</v>
+        <v>3086123740686</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
-        <v>6186471009</v>
+        <v>4310224034658</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
-        <v>5271273001</v>
+        <v>3600524030780</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
-        <v>5938220003</v>
+        <v>4063528058973</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
-        <v>4982408005</v>
+        <v>745178575799</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
-        <v>1576800007</v>
+        <v>3600540871565</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
-        <v>237598002</v>
+        <v>4002441020193</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
-        <v>6617397001</v>
+        <v>9120133546761</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
-        <v>3613616008</v>
+        <v>3600542153065</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
-        <v>237578008</v>
+        <v>4002441020278</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
-        <v>6325865003</v>
+        <v>4059729488244</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
-        <v>6003986002</v>
+        <v>4310224028671</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
-        <v>5730526006</v>
+        <v>5054563949363</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
-        <v>4714474001</v>
+        <v>3600542383455</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
-        <v>747354006</v>
+        <v>4008496559435</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
-        <v>3595212003</v>
+        <v>4251232284348</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
-        <v>5266557004</v>
+        <v>3600542466547</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
-        <v>5416680006</v>
+        <v>4003583214136</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
-        <v>5730914009</v>
+        <v>4007519026817</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
-        <v>5572101007</v>
+        <v>4311536527319</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
-        <v>4353108006</v>
+        <v>4260545852960</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
-        <v>4406782001</v>
+        <v>4100250006534</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
-        <v>6226931003</v>
+        <v>4009932137606</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
-        <v>6225434004</v>
+        <v>4003087442059</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
-        <v>4510729008</v>
+        <v>4008491224482</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
-        <v>6685273009</v>
+        <v>9783845127897</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
-        <v>6400387008</v>
+        <v>4260522560819</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
-        <v>6548710005</v>
+        <v>4006000099231</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
-        <v>6366353006</v>
+        <v>7610099050058</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
-        <v>5640553006</v>
+        <v>4250752204782</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
-        <v>4182878008</v>
+        <v>3600523814053</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
-        <v>5526330000</v>
+        <v>4008137005031</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
-        <v>3962705006</v>
+        <v>4007573242666</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
-        <v>5818602008</v>
+        <v>4250031315758</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
-        <v>3063826004</v>
+        <v>3600541901759</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
-        <v>3165324008</v>
+        <v>4260311980880</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
-        <v>3826569007</v>
+        <v>4008953173556</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
-        <v>6565641005</v>
+        <v>4262354077800</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
-        <v>4954550000</v>
+        <v>4104420230408</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
-        <v>3835268001</v>
+        <v>4006581021065</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
-        <v>6491644004</v>
+        <v>7611916164514</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
-        <v>4665373008</v>
+        <v>5000204206210</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
-        <v>4639109000</v>
+        <v>4311596625024</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
-        <v>5837783007</v>
+        <v>4000417101228</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
-        <v>4464440006</v>
+        <v>4009932131253</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
-        <v>6409434000</v>
+        <v>4311596016280</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
-        <v>4615565000</v>
+        <v>3600531629106</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
-        <v>5636352006</v>
+        <v>3600542518970</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
-        <v>6102548000</v>
+        <v>3600524123062</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
-        <v>6684989004</v>
+        <v>8006530018029</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
-        <v>3949192003</v>
+        <v>3600523718207</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
-        <v>5733504005</v>
+        <v>4260702188239</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
-        <v>6188782002</v>
+        <v>4063528079275</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
-        <v>3303667002</v>
+        <v>3600541979994</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
-        <v>4213049001</v>
+        <v>4014400929065</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
-        <v>4784743003</v>
+        <v>4311536138270</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
-        <v>5152169003</v>
+        <v>4260465568033</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
-        <v>5730544004</v>
+        <v>5054563949424</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
-        <v>3507493003</v>
+        <v>30095427</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
-        <v>3514701009</v>
+        <v>4001499943782</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
-        <v>3047848002</v>
+        <v>4260401175004</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
-        <v>5929028005</v>
+        <v>4310224028176</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
-        <v>2762565009</v>
+        <v>8004192103107</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
-        <v>2317329009</v>
+        <v>4103040002150</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
-        <v>6617339005</v>
+        <v>4021457661138</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
-        <v>6513172003</v>
+        <v>3616305729026</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
-        <v>2521764005</v>
+        <v>3600522471691</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
-        <v>5640781009</v>
+        <v>4009049541310</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
-        <v>6338890005</v>
+        <v>4260697377137</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A312" s="1">
-        <v>6005405004</v>
+        <v>4262395460036</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A313" s="1">
-        <v>2251399009</v>
+        <v>5411188112501</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A314" s="1">
-        <v>3507681008</v>
+        <v>30095656</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A315" s="1">
-        <v>5957405003</v>
+        <v>4311536012518</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
-        <v>3948563008</v>
+        <v>3600542222693</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
-        <v>6364460007</v>
+        <v>3600551156668</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
-        <v>4353138007</v>
+        <v>4260545850041</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
-        <v>5457730001</v>
+        <v>4062700636558</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
-        <v>1400084007</v>
+        <v>4008455047614</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
-        <v>5988338008</v>
+        <v>4251650812369</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
-        <v>1230152002</v>
+        <v>4001669183024</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
-        <v>1337895002</v>
+        <v>4015533004643</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
-        <v>5430127006</v>
+        <v>3600542488037</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
-        <v>6777065008</v>
+        <v>4250031314003</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
-        <v>4640880002</v>
+        <v>4311596636655</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
-        <v>1514124002</v>
+        <v>4013320214817</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
-        <v>3998049002</v>
+        <v>4016083003759</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
-        <v>2285396003</v>
+        <v>4048882126254</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
-        <v>6360811009</v>
+        <v>4008953645077</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
-        <v>5817086009</v>
+        <v>9120124604500</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
-        <v>5850643003</v>
+        <v>17854100466</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
-        <v>4896174005</v>
+        <v>4310224049348</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
-        <v>6627567005</v>
+        <v>3600531702212</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
-        <v>6220795001</v>
+        <v>4310224035594</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
-        <v>747357005</v>
+        <v>4008496559862</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
-        <v>5630645007</v>
+        <v>3600524070755</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
-        <v>4695415002</v>
+        <v>8001841923727</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
-        <v>6567769008</v>
+        <v>4062700836613</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
-        <v>4190495008</v>
+        <v>4104420218284</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
-        <v>1381665000</v>
+        <v>4006160822434</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
-        <v>4353106000</v>
+        <v>4260545850126</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
-        <v>6364455005</v>
+        <v>3600551156682</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
-        <v>6367273004</v>
+        <v>3600551158341</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
-        <v>796762005</v>
+        <v>3600520982540</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
-        <v>6252936007</v>
+        <v>5065003990180</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
-        <v>6137641004</v>
+        <v>8809959693170</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
-        <v>2797520002</v>
+        <v>4048882252540</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
-        <v>4594781004</v>
+        <v>852598003228</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
-        <v>4283538005</v>
+        <v>8714207441000</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
-        <v>6261498004</v>
+        <v>4260708710403</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
-        <v>237565002</v>
+        <v>4008455003030</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
-        <v>2521692001</v>
+        <v>3600522471684</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
-        <v>126729005</v>
+        <v>4015000010511</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
-        <v>4350472005</v>
+        <v>8718951313767</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
-        <v>6049730007</v>
+        <v>4250031353767</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
-        <v>5609235000</v>
+        <v>3600531666651</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
-        <v>3834474001</v>
+        <v>4015637827094</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
-        <v>237581004</v>
+        <v>4002441020254</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
-        <v>3493907009</v>
+        <v>4260439989154</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
-        <v>2305600002</v>
+        <v>4250587742053</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
-        <v>5101889002</v>
+        <v>4311596652082</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
-        <v>4331711006</v>
+        <v>4104420208254</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
-        <v>4525585002</v>
+        <v>3600531622787</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
-        <v>246327006</v>
+        <v>4084200857301</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
-        <v>5636333005</v>
+        <v>3600542519014</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
-        <v>5051013009</v>
+        <v>4311536513275</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
-        <v>5043132008</v>
+        <v>4012758302233</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
-        <v>6627584000</v>
+        <v>3600531702205</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
-        <v>5399453002</v>
+        <v>3600542461429</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
-        <v>6704506006</v>
+        <v>4250519680828</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
-        <v>6224089005</v>
+        <v>3337875814652</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
-        <v>3377561006</v>
+        <v>40267470</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
-        <v>6137628001</v>
+        <v>4040369951274</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
-        <v>6005422009</v>
+        <v>4262395460074</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
-        <v>3119092001</v>
+        <v>4104420028586</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
-        <v>6559232000</v>
+        <v>4270004517798</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
-        <v>5407776002</v>
+        <v>3600531662394</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
-        <v>5732213009</v>
+        <v>4014531816395</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
-        <v>6675633000</v>
+        <v>4260697146160</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
-        <v>3979691006</v>
+        <v>4104420216662</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
-        <v>6341877008</v>
+        <v>7340001805932</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
-        <v>5220883004</v>
+        <v>42428947</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
-        <v>2403700004</v>
+        <v>3600541375369</v>
       </c>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
-        <v>4382222009</v>
+        <v>4311596622504</v>
       </c>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
-        <v>4383331005</v>
+        <v>3600523900664</v>
       </c>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
-        <v>3996993004</v>
+        <v>3532678588551</v>
       </c>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
-        <v>3643475000</v>
+        <v>8711269946931</v>
       </c>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
-        <v>5587179002</v>
+        <v>3600524066512</v>
       </c>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
-        <v>1464914003</v>
+        <v>3600541043015</v>
       </c>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
-        <v>5974192005</v>
+        <v>5010724000434</v>
       </c>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
-        <v>6023258008</v>
+        <v>3616305448286</v>
       </c>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
-        <v>6644889007</v>
+        <v>4021457661107</v>
       </c>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
-        <v>6645836006</v>
+        <v>9120134225986</v>
       </c>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
-        <v>6049333000</v>
+        <v>4049713112293</v>
       </c>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
-        <v>3467986003</v>
+        <v>719346648837</v>
       </c>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
-        <v>6005412002</v>
+        <v>4262395460012</v>
       </c>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
-        <v>1021341008</v>
+        <v>4000158740526</v>
       </c>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
-        <v>5219918009</v>
+        <v>4023103201200</v>
       </c>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
-        <v>4353109009</v>
+        <v>4260545850188</v>
       </c>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
-        <v>4602812007</v>
+        <v>4310224017026</v>
       </c>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
-        <v>1301353004</v>
+        <v>4008617009382</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
-        <v>126657001</v>
+        <v>40161334</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
-        <v>6018493007</v>
+        <v>4280001939318</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
-        <v>3203253008</v>
+        <v>4008137002511</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
-        <v>6586376001</v>
+        <v>3600524202361</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
-        <v>6587285009</v>
+        <v>4262483042441</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
-        <v>5302727006</v>
+        <v>9120112221443</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
-        <v>5051121009</v>
+        <v>4311536513138</v>
       </c>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
-        <v>4899473008</v>
+        <v>4260519422441</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
-        <v>6227255009</v>
+        <v>30164635</v>
       </c>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
-        <v>3508069007</v>
+        <v>30095540</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
-        <v>5636334008</v>
+        <v>3600542519076</v>
       </c>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
-        <v>3623486006</v>
+        <v>42116455</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
-        <v>6499929006</v>
+        <v>3600524192570</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A416" s="1">
-        <v>5381021008</v>
+        <v>3616303321925</v>
       </c>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A417" s="1">
-        <v>6138768001</v>
+        <v>4040369951823</v>
       </c>
     </row>
     <row r="418" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A418" s="1">
-        <v>3868258004</v>
+        <v>4260044268026</v>
       </c>
     </row>
     <row r="419" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A419" s="1">
-        <v>4977852006</v>
+        <v>4260708710007</v>
       </c>
     </row>
     <row r="420" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A420" s="1">
-        <v>3562772000</v>
+        <v>3614225249303</v>
       </c>
     </row>
     <row r="421" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A421" s="1">
-        <v>5778386002</v>
+        <v>3600542541398</v>
       </c>
     </row>
     <row r="422" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A422" s="1">
-        <v>5491885000</v>
+        <v>3600542511070</v>
       </c>
     </row>
     <row r="423" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A423" s="1">
-        <v>6636567009</v>
+        <v>4262391990025</v>
       </c>
     </row>
     <row r="424" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A424" s="1">
-        <v>5384403005</v>
+        <v>3600524043735</v>
       </c>
     </row>
     <row r="425" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A425" s="1">
-        <v>2152369002</v>
+        <v>4012824400160</v>
       </c>
     </row>
     <row r="426" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A426" s="1">
-        <v>5980986007</v>
+        <v>3574661591667</v>
       </c>
     </row>
     <row r="427" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A427" s="1">
-        <v>6423873007</v>
+        <v>5050456009688</v>
       </c>
     </row>
     <row r="428" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A428" s="1">
-        <v>4930145006</v>
+        <v>3600524000110</v>
       </c>
     </row>
     <row r="429" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A429" s="1">
-        <v>3382940007</v>
+        <v>3600531396923</v>
       </c>
     </row>
     <row r="430" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A430" s="1">
-        <v>2623074004</v>
+        <v>3600540038401</v>
       </c>
     </row>
     <row r="431" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A431" s="1">
-        <v>5029181004</v>
+        <v>4260390244477</v>
       </c>
     </row>
     <row r="432" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A432" s="1">
-        <v>2149201001</v>
+        <v>4012824401648</v>
       </c>
     </row>
     <row r="433" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A433" s="1">
-        <v>6366381001</v>
+        <v>7610099050027</v>
       </c>
     </row>
     <row r="434" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A434" s="1">
-        <v>3109753002</v>
+        <v>4044186481044</v>
       </c>
     </row>
     <row r="435" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A435" s="1">
-        <v>4449974005</v>
+        <v>4008617040293</v>
       </c>
     </row>
     <row r="436" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A436" s="1">
-        <v>4675951009</v>
+        <v>3600542397735</v>
       </c>
     </row>
     <row r="437" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A437" s="1">
-        <v>6635035004</v>
+        <v>3600531701802</v>
       </c>
     </row>
     <row r="438" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A438" s="1">
-        <v>1464905009</v>
+        <v>3600541043060</v>
       </c>
     </row>
     <row r="439" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A439" s="1">
-        <v>4731071001</v>
+        <v>4059729307569</v>
       </c>
     </row>
     <row r="440" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A440" s="1">
-        <v>2152396004</v>
+        <v>4012824401730</v>
       </c>
     </row>
     <row r="441" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A441" s="1">
-        <v>6360836008</v>
+        <v>4008953101054</v>
       </c>
     </row>
     <row r="442" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A442" s="1">
-        <v>4233839000</v>
+        <v>48526007813</v>
       </c>
     </row>
     <row r="443" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A443" s="1">
-        <v>4525595009</v>
+        <v>3600531622985</v>
       </c>
     </row>
     <row r="444" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A444" s="1">
-        <v>6227229000</v>
+        <v>3600524136987</v>
       </c>
     </row>
     <row r="445" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A445" s="1">
-        <v>5587691007</v>
+        <v>4049713112354</v>
       </c>
     </row>
     <row r="446" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A446" s="1">
-        <v>3062370003</v>
+        <v>5060337500401</v>
       </c>
     </row>
     <row r="447" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A447" s="1">
-        <v>4353135008</v>
+        <v>4260545850003</v>
       </c>
     </row>
     <row r="448" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A448" s="1">
-        <v>4353137004</v>
+        <v>4260545850140</v>
       </c>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A449" s="1">
-        <v>3466515002</v>
+        <v>4103040019349</v>
       </c>
     </row>
     <row r="450" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A450" s="1">
-        <v>121931001</v>
+        <v>4001257218503</v>
       </c>
     </row>
     <row r="451" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A451" s="1">
-        <v>5384249003</v>
+        <v>3600524043636</v>
       </c>
     </row>
     <row r="452" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A452" s="1">
-        <v>6654415007</v>
+        <v>4008258464007</v>
       </c>
     </row>
     <row r="453" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A453" s="1">
-        <v>4130215002</v>
+        <v>4029679997011</v>
       </c>
     </row>
     <row r="454" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A454" s="1">
-        <v>5621972002</v>
+        <v>4260486333924</v>
       </c>
     </row>
     <row r="455" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A455" s="1">
-        <v>3488180000</v>
+        <v>7321011819812</v>
       </c>
     </row>
     <row r="456" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A456" s="1">
-        <v>6676006007</v>
+        <v>3600523827756</v>
       </c>
     </row>
     <row r="457" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A457" s="1">
-        <v>3508524009</v>
+        <v>30095328</v>
       </c>
     </row>
     <row r="458" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A458" s="1">
-        <v>6005370009</v>
+        <v>4262395460050</v>
       </c>
     </row>
     <row r="459" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A459" s="1">
-        <v>5707832008</v>
+        <v>30147607</v>
       </c>
     </row>
     <row r="460" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A460" s="1">
-        <v>6499940003</v>
+        <v>3600524192594</v>
       </c>
     </row>
     <row r="461" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A461" s="1">
-        <v>5236766005</v>
+        <v>4021457645497</v>
       </c>
     </row>
     <row r="462" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A462" s="1">
-        <v>2273038007</v>
+        <v>3600541278981</v>
       </c>
     </row>
     <row r="463" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A463" s="1">
-        <v>5735897000</v>
+        <v>4005900695826</v>
       </c>
     </row>
     <row r="464" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A464" s="1">
-        <v>6765968005</v>
+        <v>4250031314010</v>
       </c>
     </row>
     <row r="465" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A465" s="1">
-        <v>6730033002</v>
+        <v>4262391990506</v>
       </c>
     </row>
     <row r="466" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A466" s="1">
-        <v>452431007</v>
+        <v>4002441020308</v>
       </c>
     </row>
     <row r="467" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A467" s="1">
-        <v>6636591002</v>
+        <v>4262391990018</v>
       </c>
     </row>
     <row r="468" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A468" s="1">
-        <v>5421252007</v>
+        <v>4036581536207</v>
       </c>
     </row>
     <row r="469" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A469" s="1">
-        <v>3821374006</v>
+        <v>4071800047812</v>
       </c>
     </row>
     <row r="470" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A470" s="1">
-        <v>6412376001</v>
+        <v>7394376621932</v>
       </c>
     </row>
     <row r="471" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A471" s="1">
-        <v>6626704009</v>
+        <v>90474903</v>
       </c>
     </row>
     <row r="472" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A472" s="1">
-        <v>6274880005</v>
+        <v>3600524150556</v>
       </c>
     </row>
     <row r="473" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A473" s="1">
-        <v>5136586002</v>
+        <v>3600542452519</v>
       </c>
     </row>
     <row r="474" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A474" s="1">
-        <v>5312502006</v>
+        <v>4014995254931</v>
       </c>
     </row>
     <row r="475" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A475" s="1">
-        <v>6499555009</v>
+        <v>4059729516299</v>
       </c>
     </row>
     <row r="476" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A476" s="1">
-        <v>5776715000</v>
+        <v>4014995269164</v>
       </c>
     </row>
     <row r="477" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A477" s="1">
-        <v>5915157003</v>
+        <v>4009932133462</v>
       </c>
     </row>
     <row r="478" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A478" s="1">
-        <v>4353110009</v>
+        <v>4260545850065</v>
       </c>
     </row>
     <row r="479" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A479" s="1">
-        <v>6520678004</v>
+        <v>4018852036234</v>
       </c>
     </row>
     <row r="480" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A480" s="1">
-        <v>6672657007</v>
+        <v>7340001807141</v>
       </c>
     </row>
     <row r="481" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A481" s="1">
-        <v>2483350009</v>
+        <v>4000799109560</v>
       </c>
     </row>
     <row r="482" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A482" s="1">
-        <v>4269613009</v>
+        <v>3600542317016</v>
       </c>
     </row>
     <row r="483" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A483" s="1">
-        <v>5725511002</v>
+        <v>5037156286458</v>
       </c>
     </row>
     <row r="484" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A484" s="1">
-        <v>6122395002</v>
+        <v>8720181418402</v>
       </c>
     </row>
     <row r="485" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A485" s="1">
-        <v>5535939005</v>
+        <v>8720294016489</v>
       </c>
     </row>
     <row r="486" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A486" s="1">
-        <v>898951008</v>
+        <v>719346218405</v>
       </c>
     </row>
     <row r="487" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A487" s="1">
-        <v>870178003</v>
+        <v>5000112548280</v>
       </c>
     </row>
     <row r="488" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A488" s="1">
-        <v>4419389002</v>
+        <v>3600523902989</v>
       </c>
     </row>
     <row r="489" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A489" s="1">
-        <v>4469214004</v>
+        <v>4311596696796</v>
       </c>
     </row>
     <row r="490" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A490" s="1">
-        <v>5899594007</v>
+        <v>3574661563398</v>
       </c>
     </row>
     <row r="491" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A491" s="1">
-        <v>6531731004</v>
+        <v>8720181601965</v>
       </c>
     </row>
     <row r="492" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A492" s="1">
-        <v>4149490005</v>
+        <v>4011700840366</v>
       </c>
     </row>
     <row r="493" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A493" s="1">
-        <v>6586393006</v>
+        <v>3600531702120</v>
       </c>
     </row>
     <row r="494" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A494" s="1">
-        <v>4424548001</v>
+        <v>8711000452684</v>
       </c>
     </row>
     <row r="495" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A495" s="1">
-        <v>3795207009</v>
+        <v>4012346205700</v>
       </c>
     </row>
     <row r="496" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A496" s="1">
-        <v>6586388004</v>
+        <v>3600524202354</v>
       </c>
     </row>
     <row r="497" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A497" s="1">
-        <v>4049415005</v>
+        <v>4260159455519</v>
       </c>
     </row>
     <row r="498" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A498" s="1">
-        <v>4226466008</v>
+        <v>3600523816262</v>
       </c>
     </row>
     <row r="499" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A499" s="1">
-        <v>4914254007</v>
+        <v>4001638529426</v>
       </c>
     </row>
     <row r="500" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A500" s="1">
-        <v>3481829007</v>
+        <v>4009800003316</v>
       </c>
     </row>
     <row r="501" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A501" s="1">
-        <v>3420899001</v>
+        <v>8711000371237</v>
       </c>
     </row>
     <row r="502" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A502" s="1">
-        <v>4399685004</v>
+        <v>4311596625031</v>
       </c>
     </row>
     <row r="503" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A503" s="1">
-        <v>6001979008</v>
+        <v>3600542567329</v>
       </c>
     </row>
     <row r="504" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A504" s="1">
-        <v>4353132009</v>
+        <v>4260545850164</v>
       </c>
     </row>
     <row r="505" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A505" s="1">
-        <v>6340613003</v>
+        <v>4260380014011</v>
       </c>
     </row>
     <row r="506" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A506" s="1">
-        <v>6367245009</v>
+        <v>3600551158396</v>
       </c>
     </row>
     <row r="507" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A507" s="1">
-        <v>6760411009</v>
+        <v>5060968414917</v>
       </c>
     </row>
     <row r="508" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A508" s="1">
-        <v>5477392007</v>
+        <v>4311596660131</v>
       </c>
     </row>
     <row r="509" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A509" s="1">
-        <v>6419289009</v>
+        <v>4005240025505</v>
       </c>
     </row>
     <row r="510" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A510" s="1">
-        <v>2148359006</v>
+        <v>4012824401211</v>
       </c>
     </row>
     <row r="511" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A511" s="1">
-        <v>6717637005</v>
+        <v>5054563260024</v>
       </c>
     </row>
     <row r="512" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A512" s="1">
-        <v>6539985003</v>
+        <v>42449515</v>
       </c>
     </row>
     <row r="513" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A513" s="1">
-        <v>6627751008</v>
+        <v>3600531702564</v>
       </c>
     </row>
     <row r="514" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A514" s="1">
-        <v>335665004</v>
+        <v>4011700449019</v>
       </c>
     </row>
     <row r="515" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A515" s="1">
-        <v>237640002</v>
+        <v>4002441020162</v>
       </c>
     </row>
     <row r="516" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A516" s="1">
-        <v>5051012006</v>
+        <v>4311536513268</v>
       </c>
     </row>
     <row r="517" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A517" s="1">
-        <v>2463157008</v>
+        <v>4250587754278</v>
       </c>
     </row>
     <row r="518" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A518" s="1">
-        <v>6257087009</v>
+        <v>3600542605625</v>
       </c>
     </row>
     <row r="519" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A519" s="1">
-        <v>6558852005</v>
+        <v>8720181557521</v>
       </c>
     </row>
     <row r="520" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A520" s="1">
-        <v>5879808009</v>
+        <v>40045221</v>
       </c>
     </row>
     <row r="521" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A521" s="1">
-        <v>235441001</v>
+        <v>4011700540013</v>
       </c>
     </row>
     <row r="522" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A522" s="1">
-        <v>3643476003</v>
+        <v>8711269946900</v>
       </c>
     </row>
     <row r="523" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A523" s="1">
-        <v>3554016006</v>
+        <v>30155831</v>
       </c>
     </row>
     <row r="524" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A524" s="1">
-        <v>6507082006</v>
+        <v>4260307628987</v>
       </c>
     </row>
     <row r="525" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A525" s="1">
-        <v>2812142004</v>
+        <v>3600541670488</v>
       </c>
     </row>
     <row r="526" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A526" s="1">
-        <v>4938650007</v>
+        <v>4008617013976</v>
       </c>
     </row>
     <row r="527" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A527" s="1">
-        <v>4631072005</v>
+        <v>4260644585271</v>
       </c>
     </row>
     <row r="528" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A528" s="1">
-        <v>2243551004</v>
+        <v>3600541250154</v>
       </c>
     </row>
     <row r="529" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A529" s="1">
-        <v>697358004</v>
+        <v>4014400908589</v>
       </c>
     </row>
     <row r="530" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A530" s="1">
-        <v>2331222005</v>
+        <v>5411188114581</v>
       </c>
     </row>
     <row r="531" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A531" s="1">
-        <v>6509350002</v>
+        <v>4006000130996</v>
       </c>
     </row>
     <row r="532" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A532" s="1">
-        <v>6483901003</v>
+        <v>4262401737022</v>
       </c>
     </row>
     <row r="533" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A533" s="1">
-        <v>4353139000</v>
+        <v>4260545850089</v>
       </c>
     </row>
     <row r="534" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A534" s="1">
-        <v>6745575003</v>
+        <v>4251099603863</v>
       </c>
     </row>
     <row r="535" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A535" s="1">
-        <v>1077650002</v>
+        <v>3600521365632</v>
       </c>
     </row>
     <row r="536" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A536" s="1">
-        <v>6393679007</v>
+        <v>4003626671018</v>
       </c>
     </row>
     <row r="537" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A537" s="1">
-        <v>3199185008</v>
+        <v>4017100365416</v>
       </c>
     </row>
     <row r="538" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A538" s="1">
-        <v>6379916007</v>
+        <v>4104420254183</v>
       </c>
     </row>
     <row r="539" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A539" s="1">
-        <v>6551744004</v>
+        <v>3600524192839</v>
       </c>
     </row>
     <row r="540" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A540" s="1">
-        <v>589045001</v>
+        <v>8713537320030</v>
       </c>
     </row>
     <row r="541" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A541" s="1">
-        <v>5605345004</v>
+        <v>4014531816104</v>
       </c>
     </row>
     <row r="542" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A542" s="1">
-        <v>5885936008</v>
+        <v>30152038</v>
       </c>
     </row>
     <row r="543" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A543" s="1">
-        <v>5822042001</v>
+        <v>4014995267696</v>
       </c>
     </row>
     <row r="544" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A544" s="1">
-        <v>2243549001</v>
+        <v>3600541250802</v>
       </c>
     </row>
     <row r="545" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A545" s="1">
-        <v>3678658009</v>
+        <v>4006938505521</v>
       </c>
     </row>
     <row r="546" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A546" s="1">
-        <v>129024006</v>
+        <v>4008496104734</v>
       </c>
     </row>
     <row r="547" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A547" s="1">
-        <v>749339003</v>
+        <v>4005906002680</v>
       </c>
     </row>
     <row r="548" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A548" s="1">
-        <v>4665913000</v>
+        <v>3600542389877</v>
       </c>
     </row>
     <row r="549" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A549" s="1">
-        <v>6132485001</v>
+        <v>4260760490527</v>
       </c>
     </row>
     <row r="550" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A550" s="1">
-        <v>5964875006</v>
+        <v>4014995637772</v>
       </c>
     </row>
     <row r="551" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A551" s="1">
-        <v>5836172000</v>
+        <v>4014995269089</v>
       </c>
     </row>
     <row r="552" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A552" s="1">
-        <v>6586389007</v>
+        <v>3600524202385</v>
       </c>
     </row>
     <row r="553" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A553" s="1">
-        <v>796753001</v>
+        <v>3600520982472</v>
       </c>
     </row>
     <row r="554" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A554" s="1">
-        <v>5739982009</v>
+        <v>3600551124803</v>
       </c>
     </row>
     <row r="555" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A555" s="1">
-        <v>5748637006</v>
+        <v>4008239584250</v>
       </c>
     </row>
     <row r="556" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A556" s="1">
-        <v>3207497008</v>
+        <v>8588004638310</v>
       </c>
     </row>
     <row r="557" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A557" s="1">
-        <v>1273362004</v>
+        <v>4008452027602</v>
       </c>
     </row>
     <row r="558" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A558" s="1">
-        <v>6562131004</v>
+        <v>3600524196851</v>
       </c>
     </row>
     <row r="559" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A559" s="1">
-        <v>4659249001</v>
+        <v>4013162028559</v>
       </c>
     </row>
     <row r="560" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A560" s="1">
-        <v>4595687006</v>
+        <v>3616301176619</v>
       </c>
     </row>
     <row r="561" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A561" s="1">
-        <v>6562116005</v>
+        <v>3600524196868</v>
       </c>
     </row>
     <row r="562" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A562" s="1">
-        <v>335664001</v>
+        <v>4011700449002</v>
       </c>
     </row>
     <row r="563" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A563" s="1">
-        <v>5460629008</v>
+        <v>9120116168065</v>
       </c>
     </row>
     <row r="564" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A564" s="1">
-        <v>2141508005</v>
+        <v>4008496747313</v>
       </c>
     </row>
     <row r="565" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A565" s="1">
-        <v>3508203005</v>
+        <v>30095526</v>
       </c>
     </row>
     <row r="566" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A566" s="1">
-        <v>4904931000</v>
+        <v>4019886079136</v>
       </c>
     </row>
     <row r="567" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A567" s="1">
-        <v>6680531007</v>
+        <v>4013283711101</v>
       </c>
     </row>
     <row r="568" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A568" s="1">
-        <v>4057030009</v>
+        <v>38097103403</v>
       </c>
     </row>
     <row r="569" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A569" s="1">
-        <v>6586402009</v>
+        <v>3600531702069</v>
       </c>
     </row>
     <row r="570" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A570" s="1">
-        <v>6076236002</v>
+        <v>3600524135430</v>
       </c>
     </row>
     <row r="571" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A571" s="1">
-        <v>5052244004</v>
+        <v>3600524012618</v>
       </c>
     </row>
     <row r="572" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A572" s="1">
-        <v>6538045001</v>
+        <v>4059729521392</v>
       </c>
     </row>
     <row r="573" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A573" s="1">
-        <v>652014004</v>
+        <v>4023103072213</v>
       </c>
     </row>
     <row r="574" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A574" s="1">
-        <v>6562560008</v>
+        <v>8720181555626</v>
       </c>
     </row>
     <row r="575" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A575" s="1">
-        <v>4516876001</v>
+        <v>4310224014384</v>
       </c>
     </row>
     <row r="576" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A576" s="1">
-        <v>2697296003</v>
+        <v>4008239288226</v>
       </c>
     </row>
     <row r="577" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A577" s="1">
-        <v>4906582008</v>
+        <v>4310224018894</v>
       </c>
     </row>
     <row r="578" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A578" s="1">
-        <v>5889683009</v>
+        <v>4262354077046</v>
       </c>
     </row>
     <row r="579" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A579" s="1">
-        <v>4306263006</v>
+        <v>30177413</v>
       </c>
     </row>
     <row r="580" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A580" s="1">
-        <v>5919054007</v>
+        <v>4049639441941</v>
       </c>
     </row>
     <row r="581" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A581" s="1">
-        <v>6144435009</v>
+        <v>30158870</v>
       </c>
     </row>
     <row r="582" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A582" s="1">
-        <v>3328833006</v>
+        <v>4017645016644</v>
       </c>
     </row>
     <row r="583" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A583" s="1">
-        <v>4914253004</v>
+        <v>4001638529402</v>
       </c>
     </row>
     <row r="584" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A584" s="1">
-        <v>5636353009</v>
+        <v>3600542518994</v>
       </c>
     </row>
     <row r="585" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A585" s="1">
-        <v>3508308009</v>
+        <v>30095465</v>
       </c>
     </row>
     <row r="586" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A586" s="1">
-        <v>5236781004</v>
+        <v>4021457645480</v>
       </c>
     </row>
     <row r="587" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A587" s="1">
-        <v>4516999003</v>
+        <v>4260018196195</v>
       </c>
     </row>
     <row r="588" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A588" s="1">
-        <v>4752674001</v>
+        <v>619659185275</v>
       </c>
     </row>
     <row r="589" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A589" s="1">
-        <v>5384402002</v>
+        <v>3600524043834</v>
       </c>
     </row>
     <row r="590" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A590" s="1">
-        <v>5471363001</v>
+        <v>4059729375612</v>
       </c>
     </row>
     <row r="591" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A591" s="1">
-        <v>6494457001</v>
+        <v>4001638580755</v>
       </c>
     </row>
     <row r="592" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A592" s="1">
-        <v>6332075006</v>
+        <v>7350113022240</v>
       </c>
     </row>
     <row r="593" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A593" s="1">
-        <v>166177008</v>
+        <v>4311605475909</v>
       </c>
     </row>
     <row r="594" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A594" s="1">
-        <v>1942389008</v>
+        <v>4009977360557</v>
       </c>
     </row>
     <row r="595" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A595" s="1">
-        <v>2529461003</v>
+        <v>4002448078678</v>
       </c>
     </row>
     <row r="596" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A596" s="1">
-        <v>3969438000</v>
+        <v>7394376616884</v>
       </c>
     </row>
     <row r="597" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A597" s="1">
-        <v>5001523006</v>
+        <v>3600542427531</v>
       </c>
     </row>
     <row r="598" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A598" s="1">
-        <v>6550187004</v>
+        <v>4311596020805</v>
       </c>
     </row>
     <row r="599" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A599" s="1">
-        <v>2970687007</v>
+        <v>4104420070240</v>
       </c>
     </row>
     <row r="600" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A600" s="1">
-        <v>3508194002</v>
+        <v>800897109035</v>
       </c>
     </row>
     <row r="601" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A601" s="1">
-        <v>3861905002</v>
+        <v>4011700364299</v>
       </c>
     </row>
     <row r="602" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A602" s="1">
-        <v>6635104009</v>
+        <v>3600531702281</v>
       </c>
     </row>
     <row r="603" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A603" s="1">
-        <v>6647094006</v>
+        <v>3600524190255</v>
       </c>
     </row>
     <row r="604" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A604" s="1">
-        <v>3509404009</v>
+        <v>30102590</v>
       </c>
     </row>
     <row r="605" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A605" s="1">
-        <v>4654237003</v>
+        <v>619659185060</v>
       </c>
     </row>
     <row r="606" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A606" s="1">
-        <v>5136555008</v>
+        <v>3600542451741</v>
       </c>
     </row>
     <row r="607" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A607" s="1">
-        <v>3102646004</v>
+        <v>4001638088848</v>
       </c>
     </row>
     <row r="608" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A608" s="1">
-        <v>6011554000</v>
+        <v>8720689003438</v>
       </c>
     </row>
     <row r="609" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A609" s="1">
-        <v>6137812004</v>
+        <v>4040369951434</v>
       </c>
     </row>
     <row r="610" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A610" s="1">
-        <v>3978411009</v>
+        <v>4071800048611</v>
       </c>
     </row>
     <row r="611" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A611" s="1">
-        <v>5849237002</v>
+        <v>7317400026442</v>
       </c>
     </row>
     <row r="612" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A612" s="1">
-        <v>237809009</v>
+        <v>4006671299008</v>
       </c>
     </row>
     <row r="613" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A613" s="1">
-        <v>4612828009</v>
+        <v>30162075</v>
       </c>
     </row>
     <row r="614" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A614" s="1">
-        <v>6627601004</v>
+        <v>3600531702250</v>
       </c>
     </row>
     <row r="615" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A615" s="1">
-        <v>235485001</v>
+        <v>4011700540051</v>
       </c>
     </row>
     <row r="616" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A616" s="1">
-        <v>4644962005</v>
+        <v>85715260048</v>
       </c>
     </row>
     <row r="617" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A617" s="1">
-        <v>1079670002</v>
+        <v>4007249478665</v>
       </c>
     </row>
     <row r="618" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A618" s="1">
-        <v>3509005006</v>
+        <v>4016083006460</v>
       </c>
     </row>
     <row r="619" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A619" s="1">
-        <v>6020137003</v>
+        <v>4251823505692</v>
       </c>
     </row>
     <row r="620" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A620" s="1">
-        <v>6647077001</v>
+        <v>3600524190248</v>
       </c>
     </row>
     <row r="621" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A621" s="1">
-        <v>5116323009</v>
+        <v>4040369939173</v>
       </c>
     </row>
     <row r="622" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A622" s="1">
-        <v>4118205005</v>
+        <v>30175518</v>
       </c>
     </row>
     <row r="623" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A623" s="1">
-        <v>4405776003</v>
+        <v>4013283705377</v>
       </c>
     </row>
     <row r="624" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A624" s="1">
-        <v>6001942006</v>
+        <v>3600524125936</v>
       </c>
     </row>
     <row r="625" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A625" s="1">
-        <v>3938052006</v>
+        <v>5012008592505</v>
       </c>
     </row>
     <row r="626" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A626" s="1">
-        <v>6671370000</v>
+        <v>7340001807158</v>
       </c>
     </row>
     <row r="627" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A627" s="1">
-        <v>6094624003</v>
+        <v>3600524125752</v>
       </c>
     </row>
     <row r="628" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A628" s="1">
-        <v>6323949004</v>
+        <v>4008666812162</v>
       </c>
     </row>
     <row r="629" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A629" s="1">
-        <v>5283908003</v>
+        <v>4072600720080</v>
       </c>
     </row>
     <row r="630" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A630" s="1">
-        <v>5817028003</v>
+        <v>8720181334030</v>
       </c>
     </row>
     <row r="631" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A631" s="1">
-        <v>3994045008</v>
+        <v>4019839835000</v>
       </c>
     </row>
     <row r="632" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A632" s="1">
-        <v>217476009</v>
+        <v>4009932004533</v>
       </c>
     </row>
     <row r="633" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A633" s="1">
-        <v>4791080007</v>
+        <v>4310224060176</v>
       </c>
     </row>
     <row r="634" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A634" s="1">
-        <v>3374992007</v>
+        <v>4104420182844</v>
       </c>
     </row>
     <row r="635" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A635" s="1">
-        <v>5928407001</v>
+        <v>9120128134904</v>
       </c>
     </row>
     <row r="636" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A636" s="1">
-        <v>5315068000</v>
+        <v>30152762</v>
       </c>
     </row>
     <row r="637" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A637" s="1">
-        <v>6628647003</v>
+        <v>30144606</v>
       </c>
     </row>
     <row r="638" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A638" s="1">
-        <v>237639002</v>
+        <v>4002441020025</v>
       </c>
     </row>
     <row r="639" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A639" s="1">
-        <v>5628226007</v>
+        <v>3600542520249</v>
       </c>
     </row>
     <row r="640" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A640" s="1">
-        <v>4405775000</v>
+        <v>4013283705339</v>
       </c>
     </row>
     <row r="641" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A641" s="1">
-        <v>5704627009</v>
+        <v>3600524075576</v>
       </c>
     </row>
     <row r="642" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A642" s="1">
-        <v>6138847003</v>
+        <v>4040369951878</v>
       </c>
     </row>
     <row r="643" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A643" s="1">
-        <v>5630654001</v>
+        <v>3600524071004</v>
       </c>
     </row>
     <row r="644" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A644" s="1">
-        <v>6203695007</v>
+        <v>4008233175379</v>
       </c>
     </row>
     <row r="645" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A645" s="1">
-        <v>6600791001</v>
+        <v>4008233180243</v>
       </c>
     </row>
     <row r="646" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A646" s="1">
-        <v>6535569003</v>
+        <v>4260717240625</v>
       </c>
     </row>
     <row r="647" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A647" s="1">
-        <v>5399306007</v>
+        <v>3600542461481</v>
       </c>
     </row>
     <row r="648" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A648" s="1">
-        <v>2668814007</v>
+        <v>4000158743053</v>
       </c>
     </row>
     <row r="649" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A649" s="1">
-        <v>6313348000</v>
+        <v>5010724003824</v>
       </c>
     </row>
     <row r="650" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A650" s="1">
-        <v>2099372008</v>
+        <v>4008491111935</v>
       </c>
     </row>
     <row r="651" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A651" s="1">
-        <v>2692402001</v>
+        <v>4008890008928</v>
       </c>
     </row>
     <row r="652" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A652" s="1">
-        <v>5418115003</v>
+        <v>4311596658930</v>
       </c>
     </row>
     <row r="653" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A653" s="1">
-        <v>128129007</v>
+        <v>4009932002133</v>
       </c>
     </row>
     <row r="654" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A654" s="1">
-        <v>4491983000</v>
+        <v>4311596694914</v>
       </c>
     </row>
     <row r="655" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A655" s="1">
-        <v>4958241001</v>
+        <v>4017645020726</v>
       </c>
     </row>
     <row r="656" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A656" s="1">
-        <v>6627742004</v>
+        <v>3600531702687</v>
       </c>
     </row>
     <row r="657" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A657" s="1">
-        <v>4958199001</v>
+        <v>4017645020719</v>
       </c>
     </row>
     <row r="658" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A658" s="1">
-        <v>6635043005</v>
+        <v>3600531699758</v>
       </c>
     </row>
     <row r="659" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A659" s="1">
-        <v>4146801002</v>
+        <v>5903067016913</v>
       </c>
     </row>
     <row r="660" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A660" s="1">
-        <v>6005411009</v>
+        <v>4262395460098</v>
       </c>
     </row>
     <row r="661" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A661" s="1">
-        <v>6711912005</v>
+        <v>4251550800695</v>
       </c>
     </row>
     <row r="662" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A662" s="1">
-        <v>5636325004</v>
+        <v>3600542519007</v>
       </c>
     </row>
     <row r="663" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A663" s="1">
-        <v>5169205006</v>
+        <v>8002270406799</v>
       </c>
     </row>
     <row r="664" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A664" s="1">
-        <v>5631420003</v>
+        <v>3600524070793</v>
       </c>
     </row>
     <row r="665" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A665" s="1">
-        <v>3654739001</v>
+        <v>3600523649457</v>
       </c>
     </row>
     <row r="666" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A666" s="1">
-        <v>4561651004</v>
+        <v>3600551043203</v>
       </c>
     </row>
     <row r="667" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A667" s="1">
-        <v>6611355009</v>
+        <v>4262354077701</v>
       </c>
     </row>
     <row r="668" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A668" s="1">
-        <v>5962560001</v>
+        <v>9120085631201</v>
       </c>
     </row>
     <row r="669" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A669" s="1">
-        <v>5289461007</v>
+        <v>4000158772282</v>
       </c>
     </row>
     <row r="670" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A670" s="1">
-        <v>2695330006</v>
+        <v>4008233129761</v>
       </c>
     </row>
     <row r="671" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A671" s="1">
-        <v>5533164003</v>
+        <v>4270000873645</v>
       </c>
     </row>
     <row r="672" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A672" s="1">
-        <v>5983036000</v>
+        <v>4071800058269</v>
       </c>
     </row>
     <row r="673" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A673" s="1">
-        <v>6651602000</v>
+        <v>4255719309562</v>
       </c>
     </row>
     <row r="674" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A674" s="1">
-        <v>4977853009</v>
+        <v>4260708710014</v>
       </c>
     </row>
     <row r="675" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A675" s="1">
-        <v>6628648006</v>
+        <v>30147157</v>
       </c>
     </row>
     <row r="676" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A676" s="1">
-        <v>6313362006</v>
+        <v>30144187</v>
       </c>
     </row>
     <row r="677" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A677" s="1">
-        <v>3571044006</v>
+        <v>3600531469498</v>
       </c>
     </row>
     <row r="678" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A678" s="1">
-        <v>5267524007</v>
+        <v>4055482236900</v>
       </c>
     </row>
     <row r="679" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A679" s="1">
-        <v>6663481008</v>
+        <v>7317400010434</v>
       </c>
     </row>
     <row r="680" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A680" s="1">
-        <v>3580348009</v>
+        <v>4260159450279</v>
       </c>
     </row>
     <row r="681" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A681" s="1">
-        <v>5990824007</v>
+        <v>30152267</v>
       </c>
     </row>
     <row r="682" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A682" s="1">
-        <v>4431769004</v>
+        <v>4005437274907</v>
       </c>
     </row>
     <row r="683" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A683" s="1">
-        <v>6261813009</v>
+        <v>4043662024362</v>
       </c>
     </row>
     <row r="684" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A684" s="1">
-        <v>4283536009</v>
+        <v>8714207410501</v>
       </c>
     </row>
     <row r="685" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A685" s="1">
-        <v>3063849007</v>
+        <v>3600541910812</v>
       </c>
     </row>
     <row r="686" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A686" s="1">
-        <v>3761814008</v>
+        <v>3614227715400</v>
       </c>
     </row>
     <row r="687" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A687" s="1">
-        <v>5381022001</v>
+        <v>3616303322625</v>
       </c>
     </row>
     <row r="688" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A688" s="1">
-        <v>6394215000</v>
+        <v>4104420255005</v>
       </c>
     </row>
     <row r="689" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A689" s="1">
-        <v>1170088001</v>
+        <v>4005906274650</v>
       </c>
     </row>
     <row r="690" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A690" s="1">
-        <v>6138788005</v>
+        <v>4040369951830</v>
       </c>
     </row>
     <row r="691" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A691" s="1">
-        <v>6633388009</v>
+        <v>4260159457292</v>
       </c>
     </row>
     <row r="692" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A692" s="1">
-        <v>6577045006</v>
+        <v>4008233178899</v>
       </c>
     </row>
     <row r="693" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A693" s="1">
-        <v>248891008</v>
+        <v>4037900021503</v>
       </c>
     </row>
     <row r="694" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A694" s="1">
-        <v>5578252002</v>
+        <v>4021457638512</v>
       </c>
     </row>
     <row r="695" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A695" s="1">
-        <v>6322964000</v>
+        <v>4262401731754</v>
       </c>
     </row>
     <row r="696" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A696" s="1">
-        <v>6137895009</v>
+        <v>4040369951649</v>
       </c>
     </row>
     <row r="697" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A697" s="1">
-        <v>6051068002</v>
+        <v>4260644048820</v>
       </c>
     </row>
     <row r="698" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A698" s="1">
-        <v>6313485008</v>
+        <v>4000445030002</v>
       </c>
     </row>
     <row r="699" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A699" s="1">
-        <v>6680207007</v>
+        <v>4008137030194</v>
       </c>
     </row>
     <row r="700" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A700" s="1">
-        <v>3742872003</v>
+        <v>4280000878502</v>
       </c>
     </row>
     <row r="701" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A701" s="1">
-        <v>6379228007</v>
+        <v>4013283792841</v>
       </c>
     </row>
     <row r="702" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A702" s="1">
-        <v>5010311009</v>
+        <v>4049639427969</v>
       </c>
     </row>
     <row r="703" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A703" s="1">
-        <v>6647078004</v>
+        <v>3600524190163</v>
       </c>
     </row>
     <row r="704" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A704" s="1">
-        <v>5855929009</v>
+        <v>4021457654185</v>
       </c>
     </row>
     <row r="705" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A705" s="1">
-        <v>6627570001</v>
+        <v>3600531702182</v>
       </c>
     </row>
     <row r="706" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A706" s="1">
-        <v>6647076008</v>
+        <v>3600524190200</v>
       </c>
     </row>
     <row r="707" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A707" s="1">
-        <v>2471085005</v>
+        <v>4001638096669</v>
       </c>
     </row>
     <row r="708" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A708" s="1">
-        <v>4914903002</v>
+        <v>4059729331113</v>
       </c>
     </row>
     <row r="709" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A709" s="1">
-        <v>3507602005</v>
+        <v>30095199</v>
       </c>
     </row>
     <row r="710" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A710" s="1">
-        <v>5755647001</v>
+        <v>4086900265509</v>
       </c>
     </row>
     <row r="711" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A711" s="1">
-        <v>3509084009</v>
+        <v>4260026694188</v>
       </c>
     </row>
     <row r="712" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A712" s="1">
-        <v>5272716006</v>
+        <v>4014995219442</v>
       </c>
     </row>
     <row r="713" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A713" s="1">
-        <v>6751215009</v>
+        <v>4055482236931</v>
       </c>
     </row>
     <row r="714" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A714" s="1">
-        <v>6137745005</v>
+        <v>4040369951380</v>
       </c>
     </row>
     <row r="715" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A715" s="1">
-        <v>5892196006</v>
+        <v>4310224028008</v>
       </c>
     </row>
     <row r="716" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A716" s="1">
-        <v>5957554004</v>
+        <v>4311536012563</v>
       </c>
     </row>
     <row r="717" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A717" s="1">
-        <v>3628806001</v>
+        <v>4018077714399</v>
       </c>
     </row>
     <row r="718" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A718" s="1">
-        <v>6293594008</v>
+        <v>7640143674138</v>
       </c>
     </row>
     <row r="719" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A719" s="1">
-        <v>6219869001</v>
+        <v>4260644048165</v>
       </c>
     </row>
     <row r="720" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A720" s="1">
-        <v>6051630001</v>
+        <v>4260307629977</v>
       </c>
     </row>
     <row r="721" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A721" s="1">
-        <v>752668004</v>
+        <v>4002221009325</v>
       </c>
     </row>
     <row r="722" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A722" s="1">
-        <v>6541974006</v>
+        <v>4068101000042</v>
       </c>
     </row>
     <row r="723" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A723" s="1">
-        <v>6620947006</v>
+        <v>4062300375260</v>
       </c>
     </row>
     <row r="724" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A724" s="1">
-        <v>4277209005</v>
+        <v>5038581087979</v>
       </c>
     </row>
     <row r="725" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A725" s="1">
-        <v>5010308003</v>
+        <v>4049639427891</v>
       </c>
     </row>
     <row r="726" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A726" s="1">
-        <v>6483237009</v>
+        <v>30189355</v>
       </c>
     </row>
     <row r="727" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A727" s="1">
-        <v>5137058005</v>
+        <v>30153066</v>
       </c>
     </row>
     <row r="728" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A728" s="1">
-        <v>6321674007</v>
+        <v>4250519669168</v>
       </c>
     </row>
     <row r="729" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A729" s="1">
-        <v>5609234007</v>
+        <v>3600531666675</v>
       </c>
     </row>
     <row r="730" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A730" s="1">
-        <v>6483597008</v>
+        <v>4262401737107</v>
       </c>
     </row>
     <row r="731" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A731" s="1">
-        <v>4057031002</v>
+        <v>38097123029</v>
       </c>
     </row>
     <row r="732" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A732" s="1">
-        <v>6719045008</v>
+        <v>9120130824275</v>
       </c>
     </row>
     <row r="733" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A733" s="1">
-        <v>4814834008</v>
+        <v>3616301640738</v>
       </c>
     </row>
     <row r="734" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A734" s="1">
-        <v>4039460008</v>
+        <v>3614227902152</v>
       </c>
     </row>
     <row r="735" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A735" s="1">
-        <v>4090932003</v>
+        <v>3600531579036</v>
       </c>
     </row>
     <row r="736" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A736" s="1">
-        <v>5855963009</v>
+        <v>4021457654192</v>
       </c>
     </row>
     <row r="737" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A737" s="1">
-        <v>6102560000</v>
+        <v>3600524126285</v>
       </c>
     </row>
     <row r="738" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A738" s="1">
-        <v>6381607009</v>
+        <v>4009300020776</v>
       </c>
     </row>
     <row r="739" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A739" s="1">
-        <v>4998906009</v>
+        <v>3600524000097</v>
       </c>
     </row>
     <row r="740" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A740" s="1">
-        <v>5130489004</v>
+        <v>4719881871727</v>
       </c>
     </row>
     <row r="741" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A741" s="1">
-        <v>752727002</v>
+        <v>4008496525423</v>
       </c>
     </row>
     <row r="742" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A742" s="1">
-        <v>262039004</v>
+        <v>4008239110077</v>
       </c>
     </row>
     <row r="743" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A743" s="1">
-        <v>1176868007</v>
+        <v>4016100810117</v>
       </c>
     </row>
     <row r="744" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A744" s="1">
-        <v>4187511003</v>
+        <v>4024884045601</v>
       </c>
     </row>
     <row r="745" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A745" s="1">
-        <v>5527516005</v>
+        <v>4750746032440</v>
       </c>
     </row>
     <row r="746" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A746" s="1">
-        <v>5707847000</v>
+        <v>30152724</v>
       </c>
     </row>
     <row r="747" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A747" s="1">
-        <v>6002016009</v>
+        <v>3600542573795</v>
       </c>
     </row>
     <row r="748" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A748" s="1">
-        <v>6614067004</v>
+        <v>4260486336161</v>
       </c>
     </row>
     <row r="749" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A749" s="1">
-        <v>5354152009</v>
+        <v>3600531662219</v>
       </c>
     </row>
     <row r="750" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A750" s="1">
-        <v>6346037003</v>
+        <v>4262425550058</v>
       </c>
     </row>
     <row r="751" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A751" s="1">
-        <v>3067435004</v>
+        <v>3600523188895</v>
       </c>
     </row>
     <row r="752" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A752" s="1">
-        <v>4277265005</v>
+        <v>5038581065946</v>
       </c>
     </row>
     <row r="753" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A753" s="1">
-        <v>4703749002</v>
+        <v>3616301893387</v>
       </c>
     </row>
     <row r="754" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A754" s="1">
-        <v>1654605003</v>
+        <v>30096622</v>
       </c>
     </row>
     <row r="755" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A755" s="1">
-        <v>6274859001</v>
+        <v>30188181</v>
       </c>
     </row>
     <row r="756" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A756" s="1">
-        <v>5272670001</v>
+        <v>4014995473820</v>
       </c>
     </row>
     <row r="757" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A757" s="1">
-        <v>5647163008</v>
+        <v>4059729402189</v>
       </c>
     </row>
     <row r="758" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A758" s="1">
-        <v>1439262003</v>
+        <v>3600530695768</v>
       </c>
     </row>
     <row r="759" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A759" s="1">
-        <v>3507787005</v>
+        <v>30095250</v>
       </c>
     </row>
     <row r="760" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A760" s="1">
-        <v>6627752001</v>
+        <v>3600531702700</v>
       </c>
     </row>
     <row r="761" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A761" s="1">
-        <v>6588266001</v>
+        <v>4262483042298</v>
       </c>
     </row>
     <row r="762" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A762" s="1">
-        <v>6642783004</v>
+        <v>9120130824619</v>
       </c>
     </row>
     <row r="763" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A763" s="1">
-        <v>4870900004</v>
+        <v>4260401412963</v>
       </c>
     </row>
     <row r="764" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A764" s="1">
-        <v>4407659005</v>
+        <v>4086900195073</v>
       </c>
     </row>
     <row r="765" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A765" s="1">
-        <v>5822041008</v>
+        <v>4014995267023</v>
       </c>
     </row>
     <row r="766" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A766" s="1">
-        <v>6137807002</v>
+        <v>4040369951441</v>
       </c>
     </row>
     <row r="767" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A767" s="1">
-        <v>6188750005</v>
+        <v>4063528073570</v>
       </c>
     </row>
     <row r="768" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A768" s="1">
-        <v>2661588000</v>
+        <v>4000799109331</v>
       </c>
     </row>
     <row r="769" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A769" s="1">
-        <v>5765633009</v>
+        <v>8720181297564</v>
       </c>
     </row>
     <row r="770" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A770" s="1">
-        <v>3612838003</v>
+        <v>4025089083351</v>
       </c>
     </row>
     <row r="771" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A771" s="1">
-        <v>5100868002</v>
+        <v>7321011967872</v>
       </c>
     </row>
     <row r="772" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A772" s="1">
-        <v>4419914002</v>
+        <v>9120085630013</v>
       </c>
     </row>
     <row r="773" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A773" s="1">
-        <v>2969458001</v>
+        <v>4104420139565</v>
       </c>
     </row>
     <row r="774" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A774" s="1">
-        <v>6627585003</v>
+        <v>3600531702267</v>
       </c>
     </row>
     <row r="775" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A775" s="1">
-        <v>6751189001</v>
+        <v>5904555047136</v>
       </c>
     </row>
     <row r="776" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A776" s="1">
-        <v>5885953003</v>
+        <v>30149502</v>
       </c>
     </row>
     <row r="777" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A777" s="1">
-        <v>6469942008</v>
+        <v>3600523989942</v>
       </c>
     </row>
     <row r="778" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A778" s="1">
-        <v>3508470003</v>
+        <v>30095168</v>
       </c>
     </row>
     <row r="779" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A779" s="1">
-        <v>6586394009</v>
+        <v>3600531702137</v>
       </c>
     </row>
     <row r="780" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A780" s="1">
-        <v>6627780006</v>
+        <v>3600531702694</v>
       </c>
     </row>
     <row r="781" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A781" s="1">
-        <v>4869415001</v>
+        <v>3616301640783</v>
       </c>
     </row>
     <row r="782" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A782" s="1">
-        <v>4869462007</v>
+        <v>3616301640943</v>
       </c>
     </row>
     <row r="783" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A783" s="1">
-        <v>5266363001</v>
+        <v>3616302462049</v>
       </c>
     </row>
     <row r="784" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A784" s="1">
-        <v>3506918004</v>
+        <v>4009890110796</v>
       </c>
     </row>
     <row r="785" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A785" s="1">
-        <v>2252304004</v>
+        <v>3607346511299</v>
       </c>
     </row>
     <row r="786" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A786" s="1">
-        <v>4301713001</v>
+        <v>3600542306942</v>
       </c>
     </row>
     <row r="787" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A787" s="1">
-        <v>4383459002</v>
+        <v>4086900185074</v>
       </c>
     </row>
     <row r="788" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A788" s="1">
-        <v>4703783002</v>
+        <v>3616301893394</v>
       </c>
     </row>
     <row r="789" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A789" s="1">
-        <v>5116313002</v>
+        <v>4040369939180</v>
       </c>
     </row>
     <row r="790" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A790" s="1">
-        <v>1464909001</v>
+        <v>3600541043046</v>
       </c>
     </row>
     <row r="791" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A791" s="1">
-        <v>6364491001</v>
+        <v>3600551159607</v>
       </c>
     </row>
     <row r="792" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A792" s="1">
-        <v>5686979000</v>
+        <v>4005394200193</v>
       </c>
     </row>
     <row r="793" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A793" s="1">
-        <v>3494329008</v>
+        <v>4025089083313</v>
       </c>
     </row>
     <row r="794" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A794" s="1">
-        <v>4958209007</v>
+        <v>4017645020733</v>
       </c>
     </row>
     <row r="795" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A795" s="1">
-        <v>5834928009</v>
+        <v>7610465900130</v>
       </c>
     </row>
     <row r="796" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A796" s="1">
-        <v>143231008</v>
+        <v>4026700450408</v>
       </c>
     </row>
     <row r="797" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A797" s="1">
-        <v>3746004000</v>
+        <v>4250519603148</v>
       </c>
     </row>
     <row r="798" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A798" s="1">
-        <v>5904405009</v>
+        <v>4006000020068</v>
       </c>
     </row>
     <row r="799" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A799" s="1">
-        <v>2722293009</v>
+        <v>4008339358973</v>
       </c>
     </row>
     <row r="800" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A800" s="1">
-        <v>2152393005</v>
+        <v>4012824400115</v>
       </c>
     </row>
     <row r="801" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A801" s="1">
-        <v>6218800009</v>
+        <v>4024884030089</v>
       </c>
     </row>
     <row r="802" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A802" s="1">
-        <v>6133661006</v>
+        <v>4013162034000</v>
       </c>
     </row>
     <row r="803" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A803" s="1">
-        <v>6172561002</v>
+        <v>4251758407054</v>
       </c>
     </row>
     <row r="804" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A804" s="1">
-        <v>4740452000</v>
+        <v>4059729312464</v>
       </c>
     </row>
     <row r="805" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A805" s="1">
-        <v>3929836002</v>
+        <v>8710522368541</v>
       </c>
     </row>
     <row r="806" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A806" s="1">
-        <v>4399767005</v>
+        <v>4017645019768</v>
       </c>
     </row>
     <row r="807" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A807" s="1">
-        <v>1278412003</v>
+        <v>4018315002813</v>
       </c>
     </row>
     <row r="808" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A808" s="1">
-        <v>6493456005</v>
+        <v>3600524187613</v>
       </c>
     </row>
     <row r="809" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A809" s="1">
-        <v>6343323002</v>
+        <v>3600531692063</v>
       </c>
     </row>
     <row r="810" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A810" s="1">
-        <v>6540955002</v>
+        <v>3600531701871</v>
       </c>
     </row>
     <row r="811" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A811" s="1">
-        <v>6562124006</v>
+        <v>3600524196882</v>
       </c>
     </row>
     <row r="812" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A812" s="1">
-        <v>4869461004</v>
+        <v>3616301640912</v>
       </c>
     </row>
     <row r="813" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A813" s="1">
-        <v>5876935001</v>
+        <v>3616304219061</v>
       </c>
     </row>
     <row r="814" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A814" s="1">
-        <v>3169981007</v>
+        <v>50544134</v>
       </c>
     </row>
     <row r="815" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A815" s="1">
-        <v>4869438004</v>
+        <v>3616301640769</v>
       </c>
     </row>
     <row r="816" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A816" s="1">
-        <v>6109687005</v>
+        <v>3616304788536</v>
       </c>
     </row>
     <row r="817" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A817" s="1">
-        <v>5822031001</v>
+        <v>4014995267092</v>
       </c>
     </row>
     <row r="818" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A818" s="1">
-        <v>4869416004</v>
+        <v>3616301640813</v>
       </c>
     </row>
     <row r="819" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A819" s="1">
-        <v>6627568008</v>
+        <v>3600531702236</v>
       </c>
     </row>
     <row r="820" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A820" s="1">
-        <v>6005413005</v>
+        <v>4262395460203</v>
       </c>
     </row>
     <row r="821" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A821" s="1">
-        <v>5950936001</v>
+        <v>4002221048546</v>
       </c>
     </row>
     <row r="822" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A822" s="1">
-        <v>6404188005</v>
+        <v>3616306872097</v>
       </c>
     </row>
     <row r="823" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A823" s="1">
-        <v>4939707005</v>
+        <v>3616302467532</v>
       </c>
     </row>
     <row r="824" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A824" s="1">
-        <v>5800971000</v>
+        <v>4021457654291</v>
       </c>
     </row>
     <row r="825" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A825" s="1">
-        <v>639194006</v>
+        <v>3600540272089</v>
       </c>
     </row>
     <row r="826" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A826" s="1">
-        <v>1337898001</v>
+        <v>4015533014260</v>
       </c>
     </row>
     <row r="827" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A827" s="1">
-        <v>6590344003</v>
+        <v>4021457661718</v>
       </c>
     </row>
     <row r="828" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A828" s="1">
-        <v>5751690003</v>
+        <v>4015637015309</v>
       </c>
     </row>
     <row r="829" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A829" s="1">
-        <v>6627720004</v>
+        <v>3600531702755</v>
       </c>
     </row>
     <row r="830" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A830" s="1">
-        <v>5116333006</v>
+        <v>4040369939203</v>
       </c>
     </row>
     <row r="831" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A831" s="1">
-        <v>6137806009</v>
+        <v>4040369951427</v>
       </c>
     </row>
     <row r="832" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A832" s="1">
-        <v>4088727000</v>
+        <v>3614228943673</v>
       </c>
     </row>
     <row r="833" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A833" s="1">
-        <v>6258334005</v>
+        <v>5903274005342</v>
       </c>
     </row>
     <row r="834" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A834" s="1">
-        <v>3508758000</v>
+        <v>4002029068203</v>
       </c>
     </row>
     <row r="835" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A835" s="1">
-        <v>6079108007</v>
+        <v>8008698043479</v>
       </c>
     </row>
     <row r="836" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A836" s="1">
-        <v>2746514009</v>
+        <v>4009800004191</v>
       </c>
     </row>
     <row r="837" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A837" s="1">
-        <v>6647091007</v>
+        <v>3600524190187</v>
       </c>
     </row>
     <row r="838" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A838" s="1">
-        <v>4731934003</v>
+        <v>4065331000323</v>
       </c>
     </row>
     <row r="839" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A839" s="1">
-        <v>3859177002</v>
+        <v>3600542154666</v>
       </c>
     </row>
     <row r="840" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A840" s="1">
-        <v>6028263005</v>
+        <v>4250073460041</v>
       </c>
     </row>
     <row r="841" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A841" s="1">
-        <v>3138582000</v>
+        <v>42305156</v>
       </c>
     </row>
     <row r="842" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A842" s="1">
-        <v>4648788001</v>
+        <v>4027800965038</v>
       </c>
     </row>
     <row r="843" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A843" s="1">
-        <v>381966007</v>
+        <v>4084200774905</v>
       </c>
     </row>
     <row r="844" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A844" s="1">
-        <v>6499933005</v>
+        <v>4005800353147</v>
       </c>
     </row>
     <row r="845" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A845" s="1">
-        <v>5889501008</v>
+        <v>4310224027889</v>
       </c>
     </row>
     <row r="846" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A846" s="1">
-        <v>6572991005</v>
+        <v>8700216623711</v>
       </c>
     </row>
     <row r="847" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A847" s="1">
-        <v>121867001</v>
+        <v>4001257154009</v>
       </c>
     </row>
     <row r="848" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A848" s="1">
-        <v>5220754007</v>
+        <v>4000281157512</v>
       </c>
     </row>
     <row r="849" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A849" s="1">
-        <v>6627807000</v>
+        <v>3600531702809</v>
       </c>
     </row>
     <row r="850" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A850" s="1">
-        <v>6627811009</v>
+        <v>3600531702816</v>
       </c>
     </row>
     <row r="851" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A851" s="1">
-        <v>5315101006</v>
+        <v>30145115</v>
       </c>
     </row>
     <row r="852" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A852" s="1">
-        <v>6343322009</v>
+        <v>3600531692032</v>
       </c>
     </row>
     <row r="853" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A853" s="1">
-        <v>5141324008</v>
+        <v>4260018196898</v>
       </c>
     </row>
     <row r="854" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A854" s="1">
-        <v>5919897006</v>
+        <v>4059729418968</v>
       </c>
     </row>
     <row r="855" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A855" s="1">
-        <v>5221748005</v>
+        <v>30145450</v>
       </c>
     </row>
     <row r="856" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A856" s="1">
-        <v>4869398007</v>
+        <v>3616301640905</v>
       </c>
     </row>
     <row r="857" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A857" s="1">
-        <v>5310448007</v>
+        <v>4008339644281</v>
       </c>
     </row>
     <row r="858" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A858" s="1">
-        <v>4869688007</v>
+        <v>3616301640851</v>
       </c>
     </row>
     <row r="859" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A859" s="1">
-        <v>3791056001</v>
+        <v>3614225257483</v>
       </c>
     </row>
     <row r="860" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A860" s="1">
-        <v>3875854004</v>
+        <v>30171336</v>
       </c>
     </row>
     <row r="861" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A861" s="1">
-        <v>6030384004</v>
+        <v>3616303407148</v>
       </c>
     </row>
     <row r="862" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A862" s="1">
-        <v>4000724001</v>
+        <v>18787242001</v>
       </c>
     </row>
     <row r="863" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A863" s="1">
-        <v>4930164007</v>
+        <v>3600524000127</v>
       </c>
     </row>
     <row r="864" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A864" s="1">
-        <v>4013724007</v>
+        <v>30175211</v>
       </c>
     </row>
     <row r="865" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A865" s="1">
-        <v>3507858006</v>
+        <v>30095229</v>
       </c>
     </row>
     <row r="866" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A866" s="1">
-        <v>3798595002</v>
+        <v>96099278</v>
       </c>
     </row>
     <row r="867" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A867" s="1">
-        <v>4574568009</v>
+        <v>3616301238478</v>
       </c>
     </row>
     <row r="868" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A868" s="1">
-        <v>3673175004</v>
+        <v>7610465868607</v>
       </c>
     </row>
     <row r="869" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A869" s="1">
-        <v>6627719004</v>
+        <v>3600531702670</v>
       </c>
     </row>
     <row r="870" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A870" s="1">
-        <v>4936627001</v>
+        <v>3600531640415</v>
       </c>
     </row>
     <row r="871" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A871" s="1">
-        <v>6576064004</v>
+        <v>3600531703035</v>
       </c>
     </row>
     <row r="872" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A872" s="1">
-        <v>3169965005</v>
+        <v>50544172</v>
       </c>
     </row>
     <row r="873" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A873" s="1">
-        <v>6512962005</v>
+        <v>3616306168619</v>
       </c>
     </row>
     <row r="874" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A874" s="1">
-        <v>5093671003</v>
+        <v>3616301640790</v>
       </c>
     </row>
     <row r="875" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A875" s="1">
-        <v>3056009009</v>
+        <v>50884858</v>
       </c>
     </row>
     <row r="876" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A876" s="1">
-        <v>5833435009</v>
+        <v>3616304782565</v>
       </c>
     </row>
     <row r="877" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A877" s="1">
-        <v>6137627008</v>
+        <v>4040369951311</v>
       </c>
     </row>
     <row r="878" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A878" s="1">
-        <v>6499591005</v>
+        <v>4059729516350</v>
       </c>
     </row>
     <row r="879" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A879" s="1">
-        <v>5636012001</v>
+        <v>3616303461973</v>
       </c>
     </row>
     <row r="880" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A880" s="1">
-        <v>6474693001</v>
+        <v>4025089004202</v>
       </c>
     </row>
     <row r="881" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A881" s="1">
-        <v>6137886005</v>
+        <v>4040369951595</v>
       </c>
     </row>
     <row r="882" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A882" s="1">
-        <v>6608838003</v>
+        <v>4015200036212</v>
       </c>
     </row>
     <row r="883" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A883" s="1">
-        <v>5427221001</v>
+        <v>4009932133530</v>
       </c>
     </row>
     <row r="884" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A884" s="1">
-        <v>3805655000</v>
+        <v>4000158773616</v>
       </c>
     </row>
     <row r="885" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A885" s="1">
-        <v>5379833000</v>
+        <v>3616303458881</v>
       </c>
     </row>
     <row r="886" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A886" s="1">
-        <v>2243548008</v>
+        <v>3600541250505</v>
       </c>
     </row>
     <row r="887" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A887" s="1">
-        <v>6607166002</v>
+        <v>4002448204299</v>
       </c>
     </row>
     <row r="888" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A888" s="1">
-        <v>5803722009</v>
+        <v>8006540796269</v>
       </c>
     </row>
     <row r="889" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A889" s="1">
-        <v>6531719004</v>
+        <v>8720181601941</v>
       </c>
     </row>
     <row r="890" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A890" s="1">
-        <v>6460308007</v>
+        <v>7630135604915</v>
       </c>
     </row>
     <row r="891" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A891" s="1">
-        <v>2243547005</v>
+        <v>3600541250253</v>
       </c>
     </row>
     <row r="892" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A892" s="1">
-        <v>5399556000</v>
+        <v>3600542461542</v>
       </c>
     </row>
     <row r="893" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A893" s="1">
-        <v>6602541004</v>
+        <v>4009932134926</v>
       </c>
     </row>
     <row r="894" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A894" s="1">
-        <v>619272001</v>
+        <v>4026700488104</v>
       </c>
     </row>
     <row r="895" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A895" s="1">
-        <v>4814173000</v>
+        <v>4310224060206</v>
       </c>
     </row>
     <row r="896" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A896" s="1">
-        <v>4875733001</v>
+        <v>9120085630020</v>
       </c>
     </row>
     <row r="897" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A897" s="1">
-        <v>5485947002</v>
+        <v>7340001804843</v>
       </c>
     </row>
     <row r="898" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A898" s="1">
-        <v>4950427009</v>
+        <v>4049639427907</v>
       </c>
     </row>
     <row r="899" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A899" s="1">
-        <v>2661322002</v>
+        <v>86100013812</v>
       </c>
     </row>
     <row r="900" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A900" s="1">
-        <v>3978776003</v>
+        <v>3600531539313</v>
       </c>
     </row>
     <row r="901" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A901" s="1">
-        <v>3430286008</v>
+        <v>96137543</v>
       </c>
     </row>
     <row r="902" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A902" s="1">
-        <v>4703774008</v>
+        <v>3616301893356</v>
       </c>
     </row>
     <row r="903" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A903" s="1">
-        <v>3463820002</v>
+        <v>18787810347</v>
       </c>
     </row>
     <row r="904" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A904" s="1">
-        <v>6227064005</v>
+        <v>731509919004</v>
       </c>
     </row>
     <row r="905" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A905" s="1">
-        <v>6378672007</v>
+        <v>30146730</v>
       </c>
     </row>
     <row r="906" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A906" s="1">
-        <v>4574586007</v>
+        <v>3616301238300</v>
       </c>
     </row>
     <row r="907" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A907" s="1">
-        <v>5855958007</v>
+        <v>4021457654222</v>
       </c>
     </row>
     <row r="908" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A908" s="1">
-        <v>6315231009</v>
+        <v>4260582730498</v>
       </c>
     </row>
     <row r="909" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A909" s="1">
-        <v>4413416005</v>
+        <v>4016083059824</v>
       </c>
     </row>
     <row r="910" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A910" s="1">
-        <v>3508175001</v>
+        <v>30095571</v>
       </c>
     </row>
     <row r="911" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A911" s="1">
-        <v>4814852006</v>
+        <v>3616301640967</v>
       </c>
     </row>
     <row r="912" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A912" s="1">
-        <v>6730060004</v>
+        <v>4262391991039</v>
       </c>
     </row>
     <row r="913" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A913" s="1">
-        <v>5711009005</v>
+        <v>3616304017469</v>
       </c>
     </row>
     <row r="914" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A914" s="1">
-        <v>4039501008</v>
+        <v>3614227902084</v>
       </c>
     </row>
     <row r="915" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A915" s="1">
-        <v>5312030006</v>
+        <v>4062300417328</v>
       </c>
     </row>
     <row r="916" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A916" s="1">
-        <v>237633004</v>
+        <v>4002441020087</v>
       </c>
     </row>
     <row r="917" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A917" s="1">
-        <v>4060730008</v>
+        <v>38097291407</v>
       </c>
     </row>
     <row r="918" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A918" s="1">
-        <v>5045272001</v>
+        <v>3616302467525</v>
       </c>
     </row>
     <row r="919" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A919" s="1">
-        <v>445842005</v>
+        <v>4001669420327</v>
       </c>
     </row>
     <row r="920" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A920" s="1">
-        <v>6362870004</v>
+        <v>4008491112154</v>
       </c>
     </row>
     <row r="921" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A921" s="1">
-        <v>1625487009</v>
+        <v>4006309024279</v>
       </c>
     </row>
     <row r="922" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A922" s="1">
-        <v>5384354004</v>
+        <v>3600524043537</v>
       </c>
     </row>
     <row r="923" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A923" s="1">
-        <v>6167142003</v>
+        <v>4021457658220</v>
       </c>
     </row>
     <row r="924" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A924" s="1">
-        <v>5610914006</v>
+        <v>3600542509428</v>
       </c>
     </row>
     <row r="925" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A925" s="1">
-        <v>3999325006</v>
+        <v>4036897205736</v>
       </c>
     </row>
     <row r="926" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A926" s="1">
-        <v>2460947004</v>
+        <v>4008233124056</v>
       </c>
     </row>
     <row r="927" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A927" s="1">
-        <v>4492155006</v>
+        <v>8720181000591</v>
       </c>
     </row>
     <row r="928" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A928" s="1">
-        <v>6742294008</v>
+        <v>4000540083224</v>
       </c>
     </row>
     <row r="929" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A929" s="1">
-        <v>6616573000</v>
+        <v>4260159457216</v>
       </c>
     </row>
     <row r="930" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A930" s="1">
-        <v>4344471007</v>
+        <v>3574661554297</v>
       </c>
     </row>
     <row r="931" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A931" s="1">
-        <v>653170006</v>
+        <v>4008666200174</v>
       </c>
     </row>
     <row r="932" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A932" s="1">
-        <v>5953773001</v>
+        <v>4064666587479</v>
       </c>
     </row>
     <row r="933" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A933" s="1">
-        <v>3217697003</v>
+        <v>4000158914262</v>
       </c>
     </row>
     <row r="934" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A934" s="1">
-        <v>5346443001</v>
+        <v>8008698027400</v>
       </c>
     </row>
     <row r="935" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A935" s="1">
-        <v>6465612008</v>
+        <v>4310224037116</v>
       </c>
     </row>
     <row r="936" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A936" s="1">
-        <v>4751247000</v>
+        <v>4000576041595</v>
       </c>
     </row>
     <row r="937" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A937" s="1">
-        <v>3999253002</v>
+        <v>4011432028810</v>
       </c>
     </row>
     <row r="938" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A938" s="1">
-        <v>4972110004</v>
+        <v>4086900277601</v>
       </c>
     </row>
     <row r="939" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A939" s="1">
-        <v>2611415008</v>
+        <v>86100013621</v>
       </c>
     </row>
     <row r="940" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A940" s="1">
-        <v>5132665002</v>
+        <v>3616303252656</v>
       </c>
     </row>
     <row r="941" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A941" s="1">
-        <v>4525484000</v>
+        <v>4251550630681</v>
       </c>
     </row>
     <row r="942" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A942" s="1">
-        <v>4000723008</v>
+        <v>18787243251</v>
       </c>
     </row>
     <row r="943" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A943" s="1">
-        <v>5974737002</v>
+        <v>4055297223249</v>
       </c>
     </row>
     <row r="944" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A944" s="1">
-        <v>4525586005</v>
+        <v>3600531622831</v>
       </c>
     </row>
     <row r="945" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A945" s="1">
-        <v>6586387001</v>
+        <v>3600524202347</v>
       </c>
     </row>
     <row r="946" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A946" s="1">
-        <v>3466111004</v>
+        <v>3600523465231</v>
       </c>
     </row>
     <row r="947" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A947" s="1">
-        <v>5961027006</v>
+        <v>4260558063797</v>
       </c>
     </row>
     <row r="948" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A948" s="1">
-        <v>5636326007</v>
+        <v>3600542518963</v>
       </c>
     </row>
     <row r="949" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A949" s="1">
-        <v>1439240003</v>
+        <v>3600530695881</v>
       </c>
     </row>
     <row r="950" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A950" s="1">
-        <v>5855937000</v>
+        <v>4021457654178</v>
       </c>
     </row>
     <row r="951" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A951" s="1">
-        <v>3510827008</v>
+        <v>800897108038</v>
       </c>
     </row>
     <row r="952" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A952" s="1">
-        <v>4958210007</v>
+        <v>4017645020702</v>
       </c>
     </row>
     <row r="953" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A953" s="1">
-        <v>5197153001</v>
+        <v>3616302977833</v>
       </c>
     </row>
     <row r="954" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A954" s="1">
-        <v>5855930009</v>
+        <v>4021457654246</v>
       </c>
     </row>
     <row r="955" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A955" s="1">
-        <v>6138872009</v>
+        <v>4040369951847</v>
       </c>
     </row>
     <row r="956" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A956" s="1">
-        <v>3344753003</v>
+        <v>50671373</v>
       </c>
     </row>
     <row r="957" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A957" s="1">
-        <v>5855957004</v>
+        <v>4021457654161</v>
       </c>
     </row>
     <row r="958" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A958" s="1">
-        <v>2460959007</v>
+        <v>4008233124384</v>
       </c>
     </row>
     <row r="959" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A959" s="1">
-        <v>5459616002</v>
+        <v>9120116168058</v>
       </c>
     </row>
     <row r="960" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A960" s="1">
-        <v>5197154004</v>
+        <v>3616302977857</v>
       </c>
     </row>
     <row r="961" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A961" s="1">
-        <v>237676001</v>
+        <v>4008393001013</v>
       </c>
     </row>
     <row r="962" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A962" s="1">
-        <v>6536286004</v>
+        <v>5037156295368</v>
       </c>
     </row>
     <row r="963" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A963" s="1">
-        <v>5666620007</v>
+        <v>4059729393807</v>
       </c>
     </row>
     <row r="964" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A964" s="1">
-        <v>2769091004</v>
+        <v>8008698012857</v>
       </c>
     </row>
     <row r="965" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A965" s="1">
-        <v>6413110006</v>
+        <v>4021457637508</v>
       </c>
     </row>
     <row r="966" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A966" s="1">
-        <v>6413115001</v>
+        <v>4021457637515</v>
       </c>
     </row>
     <row r="967" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A967" s="1">
-        <v>6227001004</v>
+        <v>4251460624633</v>
       </c>
     </row>
     <row r="968" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A968" s="1">
-        <v>5938225008</v>
+        <v>4063528061331</v>
       </c>
     </row>
     <row r="969" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A969" s="1">
-        <v>4869626009</v>
+        <v>4015100427400</v>
       </c>
     </row>
     <row r="970" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A970" s="1">
-        <v>5855966008</v>
+        <v>4021457654147</v>
       </c>
     </row>
     <row r="971" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A971" s="1">
-        <v>5152179000</v>
+        <v>4260465567920</v>
       </c>
     </row>
     <row r="972" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A972" s="1">
-        <v>4353701009</v>
+        <v>7640175742485</v>
       </c>
     </row>
     <row r="973" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A973" s="1">
-        <v>6404138000</v>
+        <v>8720294042051</v>
       </c>
     </row>
     <row r="974" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A974" s="1">
-        <v>4665782008</v>
+        <v>4009049535142</v>
       </c>
     </row>
     <row r="975" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A975" s="1">
-        <v>5903859009</v>
+        <v>4008455029719</v>
       </c>
     </row>
     <row r="976" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A976" s="1">
-        <v>3371788001</v>
+        <v>5060229014351</v>
       </c>
     </row>
   </sheetData>
